--- a/AAII_Financials/Yearly/ATEYY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ATEYY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
   <si>
     <t>ATEYY</t>
   </si>
@@ -656,195 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44651</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44286</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43921</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43555</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43190</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42825</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42460</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42094</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41729</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7098000</v>
+      </c>
+      <c r="E8" s="3">
         <v>5206800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3216500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4214100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3433100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2828100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2564000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2549000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1951200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1050900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1191500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1393200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1024800</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2531400</v>
+      </c>
+      <c r="E9" s="3">
         <v>2234600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1589900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1813900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1490500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1306500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1109600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1158900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>947600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>446000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>519200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>621900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>572900</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4566600</v>
+      </c>
+      <c r="E10" s="3">
         <v>2972200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1626600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2400100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1942700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1521600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1454400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1390100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1003600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>604800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>672300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>771300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>451900</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,50 +873,54 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>491400</v>
+      </c>
+      <c r="E12" s="3">
         <v>476800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>433000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>452100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>398600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>385900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>372400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>341600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>315800</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N12" s="3">
+      <c r="N12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="3">
         <v>254800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>299300</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,93 +960,102 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>142900</v>
+        <v>-15700</v>
       </c>
       <c r="E14" s="3">
+        <v>146600</v>
+      </c>
+      <c r="F14" s="3">
         <v>59500</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-18200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>13700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-26900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-7800</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="3">
         <v>1800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>119700</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>123500</v>
+        <v>120500</v>
       </c>
       <c r="E15" s="3">
+        <v>137100</v>
+      </c>
+      <c r="F15" s="3">
         <v>117600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>105600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>92700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>80400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>77400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>41300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>43900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>26200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>25300</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3540300</v>
+        <v>3974700</v>
       </c>
       <c r="E17" s="3">
+        <v>3536500</v>
+      </c>
+      <c r="F17" s="3">
         <v>2617300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2952600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2488300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2210800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2013900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1992400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1723500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>957200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1098900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1268500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1355900</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1666500</v>
+        <v>3123300</v>
       </c>
       <c r="E18" s="3">
+        <v>1670300</v>
+      </c>
+      <c r="F18" s="3">
         <v>599200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1261400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>944800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>617300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>550100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>556700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>227600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>93700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>92600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>124700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-331100</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1146,218 +1178,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-106000</v>
+      </c>
+      <c r="E20" s="3">
         <v>18400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>15800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-28700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-14100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>5700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-5400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>9700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>9000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-4500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>37300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>9200</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1771600</v>
+        <v>3349800</v>
       </c>
       <c r="E21" s="3">
+        <v>1788900</v>
+      </c>
+      <c r="F21" s="3">
         <v>701000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1395700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1051600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>692000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>629300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>603400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>261800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>137700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>124200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>205700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-245800</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E22" s="3">
         <v>16800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>15200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>5300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1300</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3249700</v>
+      </c>
+      <c r="E23" s="3">
         <v>1501000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>516800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1288400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>958100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>629500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>544400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>597500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>228600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>101200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>86500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>160900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-323100</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>889100</v>
+      </c>
+      <c r="E24" s="3">
         <v>424700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>105000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>307400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>239200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-1500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>46900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>83200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>58200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>37300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>50400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>600</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2360600</v>
+      </c>
+      <c r="E26" s="3">
         <v>1076300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>411800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>980900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>718900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>631000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>497500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>514300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>170500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>95700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>49200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>110400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-323700</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2360600</v>
+      </c>
+      <c r="E27" s="3">
         <v>1076300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>411800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>980900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>718900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>631000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>497500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>514300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>170400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>95700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>49200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>110400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-323500</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,9 +1580,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1565,9 +1625,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>106000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-18400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-15800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>28700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>14100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-5700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>5400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-9700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-9000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>4500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-37300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-9200</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2360600</v>
+      </c>
+      <c r="E33" s="3">
         <v>1076300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>411800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>980900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>718900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>631000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>497500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>514300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>170500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>95700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>49200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>110400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-323500</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2360600</v>
+      </c>
+      <c r="E35" s="3">
         <v>1076300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>411800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>980900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>718900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>631000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>497500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>514300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>170500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>95700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>49200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>110400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-323500</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44651</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44286</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43921</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43555</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43190</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42825</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42460</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42094</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41729</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,50 +1986,54 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2138100</v>
+      </c>
+      <c r="E41" s="3">
         <v>1753200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>705400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>643500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>960000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1348700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1186800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1082400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>979000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>642500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>627900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>832300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>632000</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1984,303 +2073,327 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1438500</v>
+      </c>
+      <c r="E43" s="3">
         <v>754800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>587500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>768400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>676500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>515600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>431500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>467300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>357100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>218700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>205800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>212900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>186900</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1457300</v>
+      </c>
+      <c r="E44" s="3">
         <v>1400400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1351300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1271900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>782400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>581700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>547800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>515300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>467300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>263500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>249300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>317400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>276600</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>226400</v>
+      </c>
+      <c r="E45" s="3">
         <v>96600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>134300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>134800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>92200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>77400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>65700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>39900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>52900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>28800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>22400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>43100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>47800</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5260300</v>
+      </c>
+      <c r="E46" s="3">
         <v>4005100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2778500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2818700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2511200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2523500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2231800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2105000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1856200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1153500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1105400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1405800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1143300</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>208700</v>
-      </c>
-      <c r="E47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3">
         <v>139100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>164600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>122800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>92300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>26600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>25800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>22700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>24400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>28200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>19200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>34300</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>764600</v>
+      </c>
+      <c r="E48" s="3">
         <v>647400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>647800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>612000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>527300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>481700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>429900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>277800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>275200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>201600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>231200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>328200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>365700</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>529900</v>
+      </c>
+      <c r="E49" s="3">
         <v>523300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>651300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>720400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>702500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>493200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>474200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>235700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>143900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>111100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>122900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>500500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>461600</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,17 +2478,20 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>8</v>
+      <c r="D52" s="3">
+        <v>464200</v>
+      </c>
+      <c r="E52" s="3">
+        <v>208700</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>8</v>
@@ -2380,33 +2499,36 @@
       <c r="G52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H52" s="3">
+      <c r="H52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I52" s="3">
         <v>2400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>70400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>59100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>75400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>100600</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7369700</v>
+      </c>
+      <c r="E54" s="3">
         <v>5704300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4437700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4515200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4073800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3821400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3306400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2748700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2396900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1561000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1546800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2329000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2105500</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,260 +2654,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>715200</v>
+        <v>593200</v>
       </c>
       <c r="E57" s="3">
+        <v>473300</v>
+      </c>
+      <c r="F57" s="3">
         <v>508200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>671500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>579300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>324600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>247300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>223200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>273800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>129200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>97800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>154400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>113200</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E58" s="3">
         <v>534200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>34000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>135000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>175200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>22500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>21100</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>281300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>101100</v>
       </c>
-      <c r="M58" s="3" t="s">
+      <c r="N58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>85300</v>
       </c>
-      <c r="O58" s="3" t="s">
+      <c r="P58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>816900</v>
+        <v>1215200</v>
       </c>
       <c r="E59" s="3">
+        <v>866100</v>
+      </c>
+      <c r="F59" s="3">
         <v>292700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>507600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>487900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>299900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>245500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>205100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>154100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>116400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>118500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>184100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>130600</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2077200</v>
+      </c>
+      <c r="E60" s="3">
         <v>2066300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>834900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1314100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1242500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>812000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>655500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>567200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>821000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>346700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>216300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>423800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>243700</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>95800</v>
+      </c>
+      <c r="E61" s="3">
         <v>90200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>590400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>247500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>182700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>84700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>83800</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
       <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>200500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>327900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>384900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>505200</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>24600</v>
+      </c>
+      <c r="E62" s="3">
         <v>16200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>9300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>10200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>10100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>15700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>24100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>34200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>12200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>275700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>314400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>318200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>291700</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2365300</v>
+      </c>
+      <c r="E66" s="3">
         <v>2321700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1587100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1741700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1647600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1286400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1155400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>955200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1223600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>822900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>858700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1126800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1040600</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4122900</v>
+      </c>
+      <c r="E72" s="3">
         <v>3271200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2349000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2401000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2304400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1942700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1485100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1136400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1178900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>766200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>773100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1203600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1197600</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5004400</v>
+      </c>
+      <c r="E76" s="3">
         <v>3382600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2850700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2773500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2426200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2535000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2151000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1793400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1173300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>738100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>688100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1202200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1064900</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44651</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44286</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43921</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43555</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43190</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42825</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42460</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42094</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41729</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2360600</v>
+      </c>
+      <c r="E81" s="3">
         <v>1076300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>411800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>980900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>718900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>631000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>497500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>514300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>170500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>95700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>49200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>110400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-323500</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>180800</v>
+        <v>142900</v>
       </c>
       <c r="E83" s="3">
+        <v>150400</v>
+      </c>
+      <c r="F83" s="3">
         <v>172600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>161000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>123300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>85000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>69300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>41100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>41900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>34800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>36500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>43200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>75700</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2108000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1909700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>216000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>528300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>649600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>613300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>617800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>404200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>266000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>106700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>56800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>208800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-34600</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-207600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-116300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-129500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-169500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-141300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-112300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-75700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-53200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-38800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-27100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-22900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-27600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-50500</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-217300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-281700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-184700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-200900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-386300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-152200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-360800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-143600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-21900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-23700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-17600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-11200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-43200</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,50 +4220,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>224900</v>
+      </c>
+      <c r="E96" s="3">
         <v>182400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>164500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>191200</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>209600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>141000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>152700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>124400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>35000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-27100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-25600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-14900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-31800</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,133 +4397,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1450000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-553000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>71100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-582500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-566000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-275000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-166500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-123900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-143500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-6800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-99500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-11100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>249200</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>46200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-34200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>37500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>21600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>34400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>7900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-18400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>7400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-19200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-9500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-29000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>57200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>42300</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>486900</v>
+      </c>
+      <c r="E102" s="3">
         <v>1040700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>139900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-233500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-268300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>194000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>72100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>144100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>81400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>66700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-89300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>243800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>213700</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
